--- a/public/plantillas/Contingencia_Asignacion.xlsx
+++ b/public/plantillas/Contingencia_Asignacion.xlsx
@@ -10,8 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asignacion" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recursos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="Camiones">OFFSET(Recursos!$A$2,0,0,MAX(1,COUNTA(Recursos!$A:$A)-1),1)</definedName>
+    <definedName name="Pilotos">OFFSET(Recursos!$B$2,0,0,MAX(1,COUNTA(Recursos!$B:$B)-1),1)</definedName>
+    <definedName name="Personal">OFFSET(Recursos!$C$2,0,0,MAX(1,COUNTA(Recursos!$C:$C)-1),1)</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Asignacion'!$A$1:$P$501</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Asignacion'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Asignacion'!$A$1:$P$31</definedName>
@@ -265,32 +269,32 @@
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>ID del camión o su placa. Obligatorio para Primer Viaje, Recarga y Revisita. Vacío en Self Service y Bolsón.</t>
+        <t>Elige el camión de la lista (ID - Placa) o escribe su ID o placa. Obligatorio para Primer Viaje, Recarga y Revisita. Vacío en Self Service y Bolsón.</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>Nombre completo, código o DPI del piloto (opcional: se puede asignar solo camión).</t>
+        <t>Elige el piloto de la lista (pilotos activos de la app) o escribe nombre, código o DPI. Opcional: se puede asignar solo camión.</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Nombre, código o DPI (opcional).</t>
+        <t>Elige de la lista (personal activo de la app) o escribe nombre, código o DPI (opcional).</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Nombre, código o DPI (opcional).</t>
+        <t>Elige de la lista o escribe nombre, código o DPI (opcional).</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>Nombre, código o DPI (opcional).</t>
+        <t>Elige de la lista o escribe nombre, código o DPI (opcional).</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
-        <t>Nombre, código o DPI (opcional).</t>
+        <t>Elige de la lista o escribe nombre, código o DPI (opcional).</t>
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
@@ -669,14 +673,14 @@
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>4. Agencia, Segmento y Tipo de Asignación se eligen de la lista desplegable.</t>
+          <t>4. Las columnas con ▼ tienen lista: haz clic en la celda y toca la flecha ▼ que aparece a la derecha.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>5. Camión: usa el ID del camión o la placa. Personal: nombre completo como está en la app, código o DPI.</t>
+          <t>5. Camión, Piloto y Auxiliares traen los recursos activos de la app (si descargaste el formato desde la app).</t>
         </is>
       </c>
     </row>
@@ -958,12 +962,12 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
@@ -982,12 +986,12 @@
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>Agencia *</t>
+          <t>Agencia * ▼</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>Segmento</t>
+          <t>Segmento ▼</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
@@ -1002,37 +1006,37 @@
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>Tipo Asignación *</t>
+          <t>Tipo Asignación * ▼</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>ID Camión o Placa</t>
+          <t>ID Camión o Placa ▼</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>Piloto</t>
+          <t>Piloto ▼</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>Auxiliar 1</t>
+          <t>Auxiliar 1 ▼</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>Auxiliar 2</t>
+          <t>Auxiliar 2 ▼</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>Auxiliar 3</t>
+          <t>Auxiliar 3 ▼</t>
         </is>
       </c>
       <c r="M1" s="9" t="inlineStr">
         <is>
-          <t>Auxiliar 4</t>
+          <t>Auxiliar 4 ▼</t>
         </is>
       </c>
       <c r="N1" s="9" t="inlineStr">
@@ -10053,14 +10057,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P501"/>
-  <dataValidations count="7">
+  <dataValidations count="13">
     <dataValidation sqref="A2:A501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Escribe la fecha como DD/MM/AAAA." type="date" operator="greaterThan">
       <formula1>DATE(2024,1,1)</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista." type="list">
+    <dataValidation sqref="C2:C501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
       <formula1>=Catalogos!$A$2:$A$25</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista." type="list">
+    <dataValidation sqref="D2:D501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
       <formula1>=Catalogos!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Escribe un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
@@ -10069,8 +10073,26 @@
     <dataValidation sqref="F2:F501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Escribe un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista." type="list">
+    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
       <formula1>=Catalogos!$C$2:$C$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="No está en la lista" error="Ese valor no está en la lista de la app. ¿Guardarlo así?" promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para elegir de los recursos de la app." type="list" errorStyle="warning">
+      <formula1>=Camiones</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="No está en la lista" error="Ese valor no está en la lista de la app. ¿Guardarlo así?" promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para elegir de los recursos de la app." type="list" errorStyle="warning">
+      <formula1>=Pilotos</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="No está en la lista" error="Ese valor no está en la lista de la app. ¿Guardarlo así?" promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para elegir de los recursos de la app." type="list" errorStyle="warning">
+      <formula1>=Personal</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="No está en la lista" error="Ese valor no está en la lista de la app. ¿Guardarlo así?" promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para elegir de los recursos de la app." type="list" errorStyle="warning">
+      <formula1>=Personal</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="No está en la lista" error="Ese valor no está en la lista de la app. ¿Guardarlo así?" promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para elegir de los recursos de la app." type="list" errorStyle="warning">
+      <formula1>=Personal</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="No está en la lista" error="Ese valor no está en la lista de la app. ¿Guardarlo así?" promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para elegir de los recursos de la app." type="list" errorStyle="warning">
+      <formula1>=Personal</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Escribe la hora como HH:MM (24 horas)." type="time" operator="between">
       <formula1>0</formula1>
@@ -10479,4 +10501,46 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Camiones (ID - Placa)</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Pilotos</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>Personal (auxiliares)</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Esta hoja la llena la app con los camiones y el personal activos al descargar el formato desde "Carga de Contingencia".</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/plantillas/Contingencia_Asignacion.xlsx
+++ b/public/plantillas/Contingencia_Asignacion.xlsx
@@ -10062,7 +10062,7 @@
       <formula1>DATE(2024,1,1)</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
-      <formula1>=Catalogos!$A$2:$A$25</formula1>
+      <formula1>=Catalogos!$A$2:$A$26</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
       <formula1>=Catalogos!$B$2:$B$5</formula1>
@@ -10112,7 +10112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -10495,6 +10495,13 @@
       <c r="A25" t="inlineStr">
         <is>
           <t>Planta Cuyotenango</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Atanasio</t>
         </is>
       </c>
     </row>

--- a/public/plantillas/Contingencia_Asignacion.xlsx
+++ b/public/plantillas/Contingencia_Asignacion.xlsx
@@ -10065,7 +10065,7 @@
       <formula1>=Catalogos!$A$2:$A$26</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
-      <formula1>=Catalogos!$B$2:$B$5</formula1>
+      <formula1>=Catalogos!$B$2:$B$7</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Escribe un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
@@ -10284,6 +10284,11 @@
           <t>Cocales</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ZV&amp;COLEGIOS</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Ruta Bolsón</t>
@@ -10304,6 +10309,11 @@
       <c r="A7" t="inlineStr">
         <is>
           <t>Cuyotenango</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>INSTITUCIONALES</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/public/plantillas/Contingencia_Asignacion.xlsx
+++ b/public/plantillas/Contingencia_Asignacion.xlsx
@@ -10065,7 +10065,7 @@
       <formula1>=Catalogos!$A$2:$A$26</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
-      <formula1>=Catalogos!$B$2:$B$7</formula1>
+      <formula1>=Catalogos!$B$2:$B$8</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Escribe un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
@@ -10333,6 +10333,11 @@
           <t>El Progreso</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Cliente Rechaza Pedido</t>

--- a/public/plantillas/Contingencia_Asignacion.xlsx
+++ b/public/plantillas/Contingencia_Asignacion.xlsx
@@ -10357,7 +10357,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>No dio tiempo de entrega (Revisita)</t>
+          <t>Pendiente Envase / Cajilla</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pedido mal Digitado</t>
+          <t>Falta de Albarán / Contraseña</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No Hizo Pedido</t>
+          <t>Refacturación</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paso Bloqueado</t>
+          <t>No dio tiempo de entrega (Revisita)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -10425,7 +10425,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ruta Bolsón (Rechazo)</t>
+          <t>Pedido mal Digitado</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pendiente Envase / Cajilla</t>
         </is>
       </c>
     </row>
@@ -10435,6 +10440,16 @@
           <t>Mercados Especiales</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>No Hizo Pedido</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Falta de Albarán / Contraseña</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10442,11 +10457,26 @@
           <t>Naranjo</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Paso Bloqueado</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Refacturación</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>Playa Grande</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ruta Bolsón (Rechazo)</t>
         </is>
       </c>
     </row>
